--- a/task1a/MTF_Loan_Ledger_extended.xlsx
+++ b/task1a/MTF_Loan_Ledger_extended.xlsx
@@ -12,6 +12,8 @@
     <sheet name="GATE_STATUS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="CHANGE_LOG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MONTHLY_RATE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GATE1_ANCHORS_ORIGINAL" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,9 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -53,9 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,28 +486,34 @@
         <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>108740</v>
+        <v>147374.9</v>
       </c>
       <c r="C2" t="n">
-        <v>57292.8</v>
+        <v>77269.8</v>
       </c>
       <c r="D2" t="n">
-        <v>51447.2</v>
+        <v>70105.10000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>13.38</v>
+        <v>18.23</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -511,28 +522,34 @@
         <v>46140</v>
       </c>
       <c r="B3" t="n">
-        <v>122147.6</v>
+        <v>167103</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>89681.66</v>
       </c>
       <c r="D3" t="n">
-        <v>173594.8</v>
+        <v>147526.44</v>
       </c>
       <c r="E3" t="n">
-        <v>45.13</v>
+        <v>38.36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -541,28 +558,34 @@
         <v>46141</v>
       </c>
       <c r="B4" t="n">
-        <v>148365.75</v>
+        <v>185369.26</v>
       </c>
       <c r="C4" t="n">
-        <v>17181.34</v>
+        <v>73280.41</v>
       </c>
       <c r="D4" t="n">
-        <v>304779.21</v>
+        <v>259615.29</v>
       </c>
       <c r="E4" t="n">
-        <v>79.23999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>125</v>
+      </c>
+      <c r="H4" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -571,28 +594,34 @@
         <v>46142</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>26650.24</v>
       </c>
       <c r="C5" t="n">
-        <v>47161.83</v>
+        <v>82413.09999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>257617.38</v>
+        <v>203852.43</v>
       </c>
       <c r="E5" t="n">
-        <v>66.98</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18.53</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -607,22 +636,28 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>257617.38</v>
+        <v>203852.43</v>
       </c>
       <c r="E6" t="n">
-        <v>66.98</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>175</v>
+      </c>
+      <c r="H6" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>39</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -637,22 +672,28 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>257617.38</v>
+        <v>203852.43</v>
       </c>
       <c r="E7" t="n">
-        <v>66.98</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>61.99</v>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -667,22 +708,28 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>257617.38</v>
+        <v>203852.43</v>
       </c>
       <c r="E8" t="n">
-        <v>66.98</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -691,28 +738,34 @@
         <v>46146</v>
       </c>
       <c r="B9" t="n">
-        <v>169300.7</v>
+        <v>207091.33</v>
       </c>
       <c r="C9" t="n">
-        <v>72628.42999999999</v>
+        <v>87529.38</v>
       </c>
       <c r="D9" t="n">
-        <v>354289.66</v>
+        <v>323414.38</v>
       </c>
       <c r="E9" t="n">
-        <v>92.12</v>
+        <v>84.09</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>123.98</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -721,28 +774,34 @@
         <v>46147</v>
       </c>
       <c r="B10" t="n">
-        <v>56207.9</v>
+        <v>88278</v>
       </c>
       <c r="C10" t="n">
-        <v>87703.42</v>
+        <v>121073.06</v>
       </c>
       <c r="D10" t="n">
-        <v>322794.14</v>
+        <v>290619.32</v>
       </c>
       <c r="E10" t="n">
-        <v>83.93000000000001</v>
+        <v>75.56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>275</v>
+      </c>
+      <c r="H10" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>61.99</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -751,28 +810,34 @@
         <v>46148</v>
       </c>
       <c r="B11" t="n">
-        <v>11743.2</v>
+        <v>17562.31</v>
       </c>
       <c r="C11" t="n">
-        <v>40510.37</v>
+        <v>49153.8</v>
       </c>
       <c r="D11" t="n">
-        <v>294026.97</v>
+        <v>259027.83</v>
       </c>
       <c r="E11" t="n">
-        <v>76.45</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>52.91</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -781,28 +846,34 @@
         <v>46149</v>
       </c>
       <c r="B12" t="n">
-        <v>87937.00999999999</v>
+        <v>114527.47</v>
       </c>
       <c r="C12" t="n">
-        <v>54443.25</v>
+        <v>84893.67</v>
       </c>
       <c r="D12" t="n">
-        <v>327520.73</v>
+        <v>288661.63</v>
       </c>
       <c r="E12" t="n">
-        <v>85.16</v>
+        <v>75.05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>71.34999999999999</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -811,28 +882,34 @@
         <v>46150</v>
       </c>
       <c r="B13" t="n">
-        <v>129785.15</v>
+        <v>145093.47</v>
       </c>
       <c r="C13" t="n">
-        <v>40899.88</v>
+        <v>18818.91</v>
       </c>
       <c r="D13" t="n">
-        <v>416406</v>
+        <v>414936.19</v>
       </c>
       <c r="E13" t="n">
-        <v>108.27</v>
+        <v>107.88</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>71.06</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -847,22 +924,28 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>416406</v>
+        <v>414936.19</v>
       </c>
       <c r="E14" t="n">
-        <v>108.27</v>
+        <v>107.88</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>175</v>
+      </c>
+      <c r="H14" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>68.40000000000001</v>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -877,22 +960,28 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>416406</v>
+        <v>414936.19</v>
       </c>
       <c r="E15" t="n">
-        <v>108.27</v>
+        <v>107.88</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -901,28 +990,34 @@
         <v>46153</v>
       </c>
       <c r="B16" t="n">
-        <v>124268.5</v>
+        <v>164400.73</v>
       </c>
       <c r="C16" t="n">
-        <v>79266.45</v>
+        <v>150342.25</v>
       </c>
       <c r="D16" t="n">
-        <v>461408.05</v>
+        <v>428994.67</v>
       </c>
       <c r="E16" t="n">
-        <v>119.97</v>
+        <v>111.54</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>152.06</v>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -931,28 +1026,34 @@
         <v>46154</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>271063.98</v>
       </c>
       <c r="C17" t="n">
-        <v>461408.05</v>
+        <v>645555.6900000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>54502.96</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>14.17</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>375</v>
+      </c>
+      <c r="H17" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>76.03</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -961,28 +1062,34 @@
         <v>46155</v>
       </c>
       <c r="B18" t="n">
-        <v>128971.5</v>
+        <v>205049.3</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>152155.6</v>
       </c>
       <c r="D18" t="n">
-        <v>128971.5</v>
+        <v>107396.66</v>
       </c>
       <c r="E18" t="n">
-        <v>33.53</v>
+        <v>27.92</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>225</v>
+      </c>
+      <c r="H18" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>91.89</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -991,28 +1098,34 @@
         <v>46156</v>
       </c>
       <c r="B19" t="n">
-        <v>24737.5</v>
+        <v>64549.7</v>
       </c>
       <c r="C19" t="n">
-        <v>153406.12</v>
+        <v>74290.62</v>
       </c>
       <c r="D19" t="n">
-        <v>302.88</v>
+        <v>97655.74000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08</v>
+        <v>25.39</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>550</v>
+      </c>
+      <c r="H19" t="n">
+        <v>649</v>
+      </c>
+      <c r="I19" t="n">
+        <v>101.26</v>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1021,28 +1134,34 @@
         <v>46157</v>
       </c>
       <c r="B20" t="n">
-        <v>16228</v>
+        <v>26601.7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>18893.4</v>
       </c>
       <c r="D20" t="n">
-        <v>16530.88</v>
+        <v>105364.04</v>
       </c>
       <c r="E20" t="n">
-        <v>4.3</v>
+        <v>27.39</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>14.41</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1176,28 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>16530.88</v>
+        <v>105364.04</v>
       </c>
       <c r="E21" t="n">
-        <v>4.3</v>
+        <v>27.39</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>175</v>
+      </c>
+      <c r="H21" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>28.32</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1087,22 +1212,28 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>16530.88</v>
+        <v>105364.04</v>
       </c>
       <c r="E22" t="n">
-        <v>4.3</v>
+        <v>27.39</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1111,28 +1242,34 @@
         <v>46160</v>
       </c>
       <c r="B23" t="n">
-        <v>11801.25</v>
+        <v>154503.7</v>
       </c>
       <c r="C23" t="n">
-        <v>28332.13</v>
+        <v>176814.83</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>83052.91</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>21.59</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>51.64</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1141,28 +1278,34 @@
         <v>46161</v>
       </c>
       <c r="B24" t="n">
-        <v>24017.4</v>
+        <v>36626.53</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>66397.37</v>
       </c>
       <c r="D24" t="n">
-        <v>24017.4</v>
+        <v>53282.07</v>
       </c>
       <c r="E24" t="n">
-        <v>6.24</v>
+        <v>13.85</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25.82</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1171,28 +1314,34 @@
         <v>46162</v>
       </c>
       <c r="B25" t="n">
-        <v>315858.05</v>
+        <v>468962.84</v>
       </c>
       <c r="C25" t="n">
-        <v>166168.31</v>
+        <v>316827.14</v>
       </c>
       <c r="D25" t="n">
-        <v>173707.14</v>
+        <v>205417.77</v>
       </c>
       <c r="E25" t="n">
-        <v>45.16</v>
+        <v>53.41</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>225</v>
+      </c>
+      <c r="H25" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>27.58</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1201,28 +1350,34 @@
         <v>46163</v>
       </c>
       <c r="B26" t="n">
-        <v>321493.03</v>
+        <v>416125.45</v>
       </c>
       <c r="C26" t="n">
-        <v>86205.48</v>
+        <v>220243.74</v>
       </c>
       <c r="D26" t="n">
-        <v>408994.69</v>
+        <v>401299.48</v>
       </c>
       <c r="E26" t="n">
-        <v>106.34</v>
+        <v>104.34</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.07</v>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1231,28 +1386,34 @@
         <v>46164</v>
       </c>
       <c r="B27" t="n">
-        <v>112215</v>
+        <v>143397.06</v>
       </c>
       <c r="C27" t="n">
-        <v>46156.1</v>
+        <v>132846.44</v>
       </c>
       <c r="D27" t="n">
-        <v>475053.59</v>
+        <v>411850.1</v>
       </c>
       <c r="E27" t="n">
-        <v>123.51</v>
+        <v>107.08</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" t="n">
+        <v>59</v>
+      </c>
+      <c r="I27" t="n">
+        <v>14.09</v>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1267,22 +1428,28 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>475053.59</v>
+        <v>411850.1</v>
       </c>
       <c r="E28" t="n">
-        <v>123.51</v>
+        <v>107.08</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>425</v>
+      </c>
+      <c r="H28" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>54.31</v>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1297,22 +1464,28 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>475053.59</v>
+        <v>411850.1</v>
       </c>
       <c r="E29" t="n">
-        <v>123.51</v>
+        <v>107.08</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1321,28 +1494,34 @@
         <v>46167</v>
       </c>
       <c r="B30" t="n">
-        <v>81767</v>
+        <v>112788.36</v>
       </c>
       <c r="C30" t="n">
-        <v>44312.82</v>
+        <v>94504.57000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>512507.76</v>
+        <v>430133.89</v>
       </c>
       <c r="E30" t="n">
-        <v>133.25</v>
+        <v>111.83</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>188.68</v>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1351,28 +1530,34 @@
         <v>46168</v>
       </c>
       <c r="B31" t="n">
-        <v>90639.95</v>
+        <v>175856.79</v>
       </c>
       <c r="C31" t="n">
-        <v>203106.7</v>
+        <v>228049.32</v>
       </c>
       <c r="D31" t="n">
-        <v>400041.02</v>
+        <v>377941.36</v>
       </c>
       <c r="E31" t="n">
-        <v>104.01</v>
+        <v>98.26000000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>94.34</v>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1381,28 +1566,34 @@
         <v>46169</v>
       </c>
       <c r="B32" t="n">
-        <v>113869.5</v>
+        <v>138725.58</v>
       </c>
       <c r="C32" t="n">
-        <v>117562.69</v>
+        <v>134544.01</v>
       </c>
       <c r="D32" t="n">
-        <v>396347.83</v>
+        <v>382122.93</v>
       </c>
       <c r="E32" t="n">
-        <v>103.05</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>675</v>
+      </c>
+      <c r="H32" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="I32" t="n">
+        <v>107.2</v>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1608,28 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>396347.83</v>
+        <v>382122.93</v>
       </c>
       <c r="E33" t="n">
-        <v>103.05</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PRE-SERIES</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>250</v>
+      </c>
+      <c r="H33" t="n">
+        <v>295</v>
+      </c>
+      <c r="I33" t="n">
+        <v>107.56</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1441,10 +1638,10 @@
         <v>46171</v>
       </c>
       <c r="B34" t="n">
-        <v>306152.1</v>
+        <v>342313.8799999999</v>
       </c>
       <c r="C34" t="n">
-        <v>131033.53</v>
+        <v>152970.41</v>
       </c>
       <c r="D34" t="n">
         <v>571466.4</v>
@@ -1457,12 +1654,18 @@
           <t>SOF-EXACT</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>94.51000000000001</v>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1484,15 +1687,21 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>425</v>
+      </c>
+      <c r="H35" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>94.51000000000001</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1514,15 +1723,21 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1531,28 +1746,34 @@
         <v>46174</v>
       </c>
       <c r="B37" t="n">
-        <v>31104.7</v>
+        <v>215452.97</v>
       </c>
       <c r="C37" t="n">
-        <v>165068.74</v>
+        <v>351675.9</v>
       </c>
       <c r="D37" t="n">
-        <v>437502.36</v>
+        <v>435243.47</v>
       </c>
       <c r="E37" t="n">
-        <v>113.75</v>
+        <v>113.16</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>195.4</v>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1561,28 +1782,34 @@
         <v>46175</v>
       </c>
       <c r="B38" t="n">
-        <v>211758</v>
+        <v>273714.22</v>
       </c>
       <c r="C38" t="n">
-        <v>153384.07</v>
+        <v>221360.84</v>
       </c>
       <c r="D38" t="n">
-        <v>495876.29</v>
+        <v>487596.85</v>
       </c>
       <c r="E38" t="n">
-        <v>128.93</v>
+        <v>126.78</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>250</v>
+      </c>
+      <c r="H38" t="n">
+        <v>295</v>
+      </c>
+      <c r="I38" t="n">
+        <v>97.7</v>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1818,34 @@
         <v>46176</v>
       </c>
       <c r="B39" t="n">
-        <v>108443.03</v>
+        <v>287873.47</v>
       </c>
       <c r="C39" t="n">
-        <v>356330.15</v>
+        <v>347435.54</v>
       </c>
       <c r="D39" t="n">
-        <v>247989.17</v>
+        <v>428034.78</v>
       </c>
       <c r="E39" t="n">
-        <v>64.48</v>
+        <v>111.29</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>675</v>
+      </c>
+      <c r="H39" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>119.33</v>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1621,28 +1854,34 @@
         <v>46177</v>
       </c>
       <c r="B40" t="n">
-        <v>255001.05</v>
+        <v>381200.76</v>
       </c>
       <c r="C40" t="n">
-        <v>39272.96</v>
+        <v>321018.31</v>
       </c>
       <c r="D40" t="n">
-        <v>463717.27</v>
+        <v>488217.23</v>
       </c>
       <c r="E40" t="n">
-        <v>120.57</v>
+        <v>126.94</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>75</v>
+      </c>
+      <c r="H40" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>109.42</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1651,10 +1890,10 @@
         <v>46178</v>
       </c>
       <c r="B41" t="n">
-        <v>189123.1</v>
+        <v>261504.05</v>
       </c>
       <c r="C41" t="n">
-        <v>74138.88</v>
+        <v>171019.79</v>
       </c>
       <c r="D41" t="n">
         <v>578701.49</v>
@@ -1667,12 +1906,18 @@
           <t>SOF-EXACT</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>675</v>
+      </c>
+      <c r="H41" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>127.95</v>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1694,15 +1939,21 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>575</v>
+      </c>
+      <c r="H42" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>101.12</v>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1724,15 +1975,21 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1741,28 +1998,34 @@
         <v>46181</v>
       </c>
       <c r="B44" t="n">
-        <v>28892.5</v>
+        <v>78251.45999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>62949.5</v>
+        <v>99264.14</v>
       </c>
       <c r="D44" t="n">
-        <v>544644.49</v>
+        <v>557688.8100000001</v>
       </c>
       <c r="E44" t="n">
-        <v>141.61</v>
+        <v>145</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>257.7</v>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1771,28 +2034,34 @@
         <v>46182</v>
       </c>
       <c r="B45" t="n">
-        <v>39440</v>
+        <v>62987.76</v>
       </c>
       <c r="C45" t="n">
-        <v>41267.77</v>
+        <v>68671.03999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>542816.72</v>
+        <v>552005.53</v>
       </c>
       <c r="E45" t="n">
-        <v>141.13</v>
+        <v>143.52</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>100</v>
+      </c>
+      <c r="H45" t="n">
+        <v>118</v>
+      </c>
+      <c r="I45" t="n">
+        <v>128.85</v>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1801,28 +2070,34 @@
         <v>46183</v>
       </c>
       <c r="B46" t="n">
-        <v>32822.9</v>
+        <v>242212.63</v>
       </c>
       <c r="C46" t="n">
-        <v>299453.71</v>
+        <v>395556.22</v>
       </c>
       <c r="D46" t="n">
-        <v>276185.9</v>
+        <v>398661.94</v>
       </c>
       <c r="E46" t="n">
-        <v>71.81</v>
+        <v>103.65</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>325</v>
+      </c>
+      <c r="H46" t="n">
+        <v>383.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>151.9</v>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1831,28 +2106,34 @@
         <v>46184</v>
       </c>
       <c r="B47" t="n">
-        <v>49443</v>
+        <v>104815.6</v>
       </c>
       <c r="C47" t="n">
-        <v>128104.21</v>
+        <v>215507.37</v>
       </c>
       <c r="D47" t="n">
-        <v>197524.69</v>
+        <v>287970.17</v>
       </c>
       <c r="E47" t="n">
-        <v>51.36</v>
+        <v>74.87</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>144.19</v>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1861,10 +2142,10 @@
         <v>46185</v>
       </c>
       <c r="B48" t="n">
-        <v>210720.2</v>
+        <v>671224.8500000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>550950.13</v>
       </c>
       <c r="D48" t="n">
         <v>408244.89</v>
@@ -1877,12 +2158,18 @@
           <t>SOF-EXACT</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>675</v>
+      </c>
+      <c r="H48" t="n">
+        <v>796.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>145.58</v>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1904,15 +2191,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>225</v>
+      </c>
+      <c r="H49" t="n">
+        <v>265.5</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1934,15 +2227,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1951,28 +2250,34 @@
         <v>46188</v>
       </c>
       <c r="B51" t="n">
-        <v>53565.5</v>
+        <v>78928.60000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>21075.8</v>
+        <v>47884.25</v>
       </c>
       <c r="D51" t="n">
-        <v>440734.59</v>
+        <v>439289.24</v>
       </c>
       <c r="E51" t="n">
-        <v>114.59</v>
+        <v>114.22</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>248.25</v>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -1981,28 +2286,34 @@
         <v>46189</v>
       </c>
       <c r="B52" t="n">
-        <v>156164.45</v>
+        <v>226752.28</v>
       </c>
       <c r="C52" t="n">
-        <v>84075.31</v>
+        <v>187438.92</v>
       </c>
       <c r="D52" t="n">
-        <v>512823.73</v>
+        <v>478602.6</v>
       </c>
       <c r="E52" t="n">
-        <v>133.33</v>
+        <v>124.44</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>300</v>
+      </c>
+      <c r="H52" t="n">
+        <v>354</v>
+      </c>
+      <c r="I52" t="n">
+        <v>76.13</v>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2011,28 +2322,34 @@
         <v>46190</v>
       </c>
       <c r="B53" t="n">
-        <v>369249.7</v>
+        <v>544387.3400000001</v>
       </c>
       <c r="C53" t="n">
-        <v>167812.18</v>
+        <v>396133.6300000001</v>
       </c>
       <c r="D53" t="n">
-        <v>714261.25</v>
+        <v>626856.3100000001</v>
       </c>
       <c r="E53" t="n">
-        <v>185.71</v>
+        <v>162.98</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>75</v>
+      </c>
+      <c r="H53" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>104.96</v>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2041,28 +2358,34 @@
         <v>46191</v>
       </c>
       <c r="B54" t="n">
-        <v>254356.55</v>
+        <v>376145.53</v>
       </c>
       <c r="C54" t="n">
-        <v>325923.91</v>
+        <v>416700.23</v>
       </c>
       <c r="D54" t="n">
-        <v>642693.89</v>
+        <v>586301.61</v>
       </c>
       <c r="E54" t="n">
-        <v>167.1</v>
+        <v>152.44</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>300</v>
+      </c>
+      <c r="H54" t="n">
+        <v>354</v>
+      </c>
+      <c r="I54" t="n">
+        <v>110.7</v>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2071,10 +2394,10 @@
         <v>46192</v>
       </c>
       <c r="B55" t="n">
-        <v>232152.3</v>
+        <v>302028.98</v>
       </c>
       <c r="C55" t="n">
-        <v>183340.92</v>
+        <v>196825.32</v>
       </c>
       <c r="D55" t="n">
         <v>691505.27</v>
@@ -2087,12 +2410,18 @@
           <t>SOF-EXACT</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>425</v>
+      </c>
+      <c r="H55" t="n">
+        <v>501.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>125.83</v>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2114,15 +2443,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>150</v>
+      </c>
+      <c r="H56" t="n">
+        <v>177</v>
+      </c>
+      <c r="I56" t="n">
+        <v>165.5</v>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2144,15 +2479,21 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2161,28 +2502,34 @@
         <v>46195</v>
       </c>
       <c r="B58" t="n">
-        <v>90292.5</v>
+        <v>180523.69</v>
       </c>
       <c r="C58" t="n">
-        <v>137107.52</v>
+        <v>176112.85</v>
       </c>
       <c r="D58" t="n">
-        <v>644690.25</v>
+        <v>695916.11</v>
       </c>
       <c r="E58" t="n">
-        <v>167.62</v>
+        <v>180.94</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>316.28</v>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2191,28 +2538,34 @@
         <v>46196</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>262309.59</v>
       </c>
       <c r="C59" t="n">
-        <v>170772.42</v>
+        <v>447811.65</v>
       </c>
       <c r="D59" t="n">
-        <v>473917.83</v>
+        <v>510414.05</v>
       </c>
       <c r="E59" t="n">
-        <v>123.22</v>
+        <v>132.71</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>350</v>
+      </c>
+      <c r="H59" t="n">
+        <v>413</v>
+      </c>
+      <c r="I59" t="n">
+        <v>158.14</v>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2221,28 +2574,34 @@
         <v>46197</v>
       </c>
       <c r="B60" t="n">
-        <v>160468.25</v>
+        <v>198327.86</v>
       </c>
       <c r="C60" t="n">
-        <v>56123.11</v>
+        <v>148731.02</v>
       </c>
       <c r="D60" t="n">
-        <v>578262.98</v>
+        <v>560010.89</v>
       </c>
       <c r="E60" t="n">
-        <v>150.35</v>
+        <v>145.6</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>525</v>
+      </c>
+      <c r="H60" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="I60" t="n">
+        <v>186.45</v>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2251,10 +2610,10 @@
         <v>46198</v>
       </c>
       <c r="B61" t="n">
-        <v>47218.7</v>
+        <v>206474</v>
       </c>
       <c r="C61" t="n">
-        <v>84623.98</v>
+        <v>225627.19</v>
       </c>
       <c r="D61" t="n">
         <v>540857.7</v>
@@ -2267,12 +2626,18 @@
           <t>SOF-EXACT</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>350</v>
+      </c>
+      <c r="H61" t="n">
+        <v>413</v>
+      </c>
+      <c r="I61" t="n">
+        <v>188.1</v>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2294,15 +2659,21 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>125</v>
+      </c>
+      <c r="H62" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>137.32</v>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2324,15 +2695,21 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" t="n">
+        <v>177</v>
+      </c>
+      <c r="I63" t="n">
+        <v>150.71</v>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2354,15 +2731,21 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2371,28 +2754,34 @@
         <v>46202</v>
       </c>
       <c r="B65" t="n">
-        <v>257660.05</v>
+        <v>370372.23</v>
       </c>
       <c r="C65" t="n">
-        <v>155256.3</v>
+        <v>257814.31</v>
       </c>
       <c r="D65" t="n">
-        <v>643261.45</v>
+        <v>653415.62</v>
       </c>
       <c r="E65" t="n">
-        <v>167.25</v>
+        <v>169.89</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>301.42</v>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2401,28 +2790,34 @@
         <v>46203</v>
       </c>
       <c r="B66" t="n">
-        <v>107171.2</v>
+        <v>156150.64</v>
       </c>
       <c r="C66" t="n">
-        <v>25835.61</v>
+        <v>118243.81</v>
       </c>
       <c r="D66" t="n">
-        <v>724597.04</v>
+        <v>691322.45</v>
       </c>
       <c r="E66" t="n">
-        <v>188.4</v>
+        <v>179.74</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>150</v>
+      </c>
+      <c r="H66" t="n">
+        <v>177</v>
+      </c>
+      <c r="I66" t="n">
+        <v>150.71</v>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2444,15 +2839,21 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+          <t>LEGACY(no SOF: 2026-07-01..07-05 uncovered)</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2474,15 +2875,21 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>INTERPOLATED</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+          <t>LEGACY(no SOF: 2026-07-01..07-05 uncovered)</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -2504,15 +2911,21 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SOF-EXACT</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+          <t>LEGACY(no SOF: 2026-07-01..07-05 uncovered)</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>NOT AVAILABLE (no SOF supplied pre-2026-07-06)</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED)</t>
         </is>
       </c>
     </row>
@@ -4831,7 +5244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4868,13 +5281,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46171</v>
+        <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>571466.4</v>
+        <v>70105.10000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>571466.4</v>
+        <v>70105.10000000001</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -4886,19 +5299,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46178</v>
+        <v>46140</v>
       </c>
       <c r="B3" t="n">
-        <v>578701.49</v>
+        <v>147526.44</v>
       </c>
       <c r="C3" t="n">
-        <v>578701.49</v>
+        <v>147526.44</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -4910,19 +5323,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46185</v>
+        <v>46141</v>
       </c>
       <c r="B4" t="n">
-        <v>408244.89</v>
+        <v>259615.29</v>
       </c>
       <c r="C4" t="n">
-        <v>408244.89</v>
+        <v>259615.29</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4934,19 +5347,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46192</v>
+        <v>46142</v>
       </c>
       <c r="B5" t="n">
-        <v>691505.27</v>
+        <v>203852.43</v>
       </c>
       <c r="C5" t="n">
-        <v>691505.27</v>
+        <v>203852.43</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -4958,19 +5371,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46198</v>
+        <v>46146</v>
       </c>
       <c r="B6" t="n">
-        <v>540857.7</v>
+        <v>323414.38</v>
       </c>
       <c r="C6" t="n">
-        <v>540857.7</v>
+        <v>323414.38</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -4982,19 +5395,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46206</v>
+        <v>46147</v>
       </c>
       <c r="B7" t="n">
-        <v>618861.6899999999</v>
+        <v>290619.32</v>
       </c>
       <c r="C7" t="n">
-        <v>618861.6899999999</v>
+        <v>290619.32</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -5006,19 +5419,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>original (2026-04-27..07-03 window)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46209</v>
+        <v>46148</v>
       </c>
       <c r="B8" t="n">
-        <v>630685.38</v>
+        <v>259027.83</v>
       </c>
       <c r="C8" t="n">
-        <v>630685.38</v>
+        <v>259027.83</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -5030,19 +5443,19 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46149</v>
       </c>
       <c r="B9" t="n">
-        <v>491387.72</v>
+        <v>288661.63</v>
       </c>
       <c r="C9" t="n">
-        <v>491387.72</v>
+        <v>288661.63</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -5054,22 +5467,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46211</v>
+        <v>46150</v>
       </c>
       <c r="B10" t="n">
-        <v>348776.67</v>
+        <v>414936.19</v>
       </c>
       <c r="C10" t="n">
-        <v>348776.67</v>
+        <v>414936.19</v>
       </c>
       <c r="D10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5078,19 +5491,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46212</v>
+        <v>46153</v>
       </c>
       <c r="B11" t="n">
-        <v>360847.88</v>
+        <v>428994.67</v>
       </c>
       <c r="C11" t="n">
-        <v>360847.88</v>
+        <v>428994.67</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -5102,19 +5515,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46213</v>
+        <v>46154</v>
       </c>
       <c r="B12" t="n">
-        <v>427360.86</v>
+        <v>54502.96</v>
       </c>
       <c r="C12" t="n">
-        <v>427360.86</v>
+        <v>54502.96</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -5126,19 +5539,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46216</v>
+        <v>46155</v>
       </c>
       <c r="B13" t="n">
-        <v>476403.1</v>
+        <v>107396.66</v>
       </c>
       <c r="C13" t="n">
-        <v>476403.1</v>
+        <v>107396.66</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -5150,19 +5563,19 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46217</v>
+        <v>46156</v>
       </c>
       <c r="B14" t="n">
-        <v>508312.92</v>
+        <v>97655.74000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>508312.92</v>
+        <v>97655.74000000001</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -5174,19 +5587,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46218</v>
+        <v>46157</v>
       </c>
       <c r="B15" t="n">
-        <v>520872.01</v>
+        <v>105364.04</v>
       </c>
       <c r="C15" t="n">
-        <v>520872.01</v>
+        <v>105364.04</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -5198,19 +5611,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46219</v>
+        <v>46160</v>
       </c>
       <c r="B16" t="n">
-        <v>597074.76</v>
+        <v>83052.91</v>
       </c>
       <c r="C16" t="n">
-        <v>597074.76</v>
+        <v>83052.91</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -5222,19 +5635,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46220</v>
+        <v>46161</v>
       </c>
       <c r="B17" t="n">
-        <v>383055.85</v>
+        <v>53282.07</v>
       </c>
       <c r="C17" t="n">
-        <v>383055.85</v>
+        <v>53282.07</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -5246,22 +5659,22 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46223</v>
+        <v>46162</v>
       </c>
       <c r="B18" t="n">
-        <v>407769.28</v>
+        <v>205417.77</v>
       </c>
       <c r="C18" t="n">
-        <v>407769.28</v>
+        <v>205417.77</v>
       </c>
       <c r="D18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5270,19 +5683,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46224</v>
+        <v>46163</v>
       </c>
       <c r="B19" t="n">
-        <v>407769.28</v>
+        <v>401299.48</v>
       </c>
       <c r="C19" t="n">
-        <v>407769.28</v>
+        <v>401299.48</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -5294,19 +5707,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46225</v>
+        <v>46164</v>
       </c>
       <c r="B20" t="n">
-        <v>394650.02</v>
+        <v>411850.1</v>
       </c>
       <c r="C20" t="n">
-        <v>394650.02</v>
+        <v>411850.1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5318,22 +5731,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46226</v>
+        <v>46167</v>
       </c>
       <c r="B21" t="n">
-        <v>281378.71</v>
+        <v>430133.89</v>
       </c>
       <c r="C21" t="n">
-        <v>281378.71</v>
+        <v>430133.89</v>
       </c>
       <c r="D21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5342,19 +5755,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46227</v>
+        <v>46168</v>
       </c>
       <c r="B22" t="n">
-        <v>187120.58</v>
+        <v>377941.36</v>
       </c>
       <c r="C22" t="n">
-        <v>187120.58</v>
+        <v>377941.36</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -5366,19 +5779,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46231</v>
+        <v>46169</v>
       </c>
       <c r="B23" t="n">
-        <v>185777.83</v>
+        <v>382122.93</v>
       </c>
       <c r="C23" t="n">
-        <v>185777.83</v>
+        <v>382122.93</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -5390,22 +5803,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46232</v>
+        <v>46171</v>
       </c>
       <c r="B24" t="n">
-        <v>191241.28</v>
+        <v>571466.4</v>
       </c>
       <c r="C24" t="n">
-        <v>191241.28</v>
+        <v>571466.4</v>
       </c>
       <c r="D24" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5414,19 +5827,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46233</v>
+        <v>46174</v>
       </c>
       <c r="B25" t="n">
-        <v>201205.73</v>
+        <v>435243.47</v>
       </c>
       <c r="C25" t="n">
-        <v>201205.73</v>
+        <v>435243.47</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -5438,19 +5851,19 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46234</v>
+        <v>46175</v>
       </c>
       <c r="B26" t="n">
-        <v>218562.88</v>
+        <v>487596.85</v>
       </c>
       <c r="C26" t="n">
-        <v>218562.88</v>
+        <v>487596.85</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -5462,19 +5875,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46237</v>
+        <v>46176</v>
       </c>
       <c r="B27" t="n">
-        <v>260072.7</v>
+        <v>428034.78</v>
       </c>
       <c r="C27" t="n">
-        <v>260072.7</v>
+        <v>428034.78</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -5486,19 +5899,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46238</v>
+        <v>46177</v>
       </c>
       <c r="B28" t="n">
-        <v>350945.98</v>
+        <v>488217.23</v>
       </c>
       <c r="C28" t="n">
-        <v>350945.98</v>
+        <v>488217.23</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5510,19 +5923,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46239</v>
+        <v>46178</v>
       </c>
       <c r="B29" t="n">
-        <v>335695.17</v>
+        <v>578701.49</v>
       </c>
       <c r="C29" t="n">
-        <v>335695.17</v>
+        <v>578701.49</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -5534,22 +5947,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="B30" t="n">
-        <v>376597.84</v>
+        <v>557688.8100000001</v>
       </c>
       <c r="C30" t="n">
-        <v>376597.84</v>
+        <v>557688.8100000001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5558,19 +5971,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46241</v>
+        <v>46182</v>
       </c>
       <c r="B31" t="n">
-        <v>385163.61</v>
+        <v>552005.53</v>
       </c>
       <c r="C31" t="n">
-        <v>385163.61</v>
+        <v>552005.53</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -5582,19 +5995,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46244</v>
+        <v>46183</v>
       </c>
       <c r="B32" t="n">
-        <v>318603.79</v>
+        <v>398661.94</v>
       </c>
       <c r="C32" t="n">
-        <v>318603.79</v>
+        <v>398661.94</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -5606,19 +6019,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>46245</v>
+        <v>46184</v>
       </c>
       <c r="B33" t="n">
-        <v>363157.68</v>
+        <v>287970.17</v>
       </c>
       <c r="C33" t="n">
-        <v>363157.68</v>
+        <v>287970.17</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -5630,19 +6043,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>46246</v>
+        <v>46185</v>
       </c>
       <c r="B34" t="n">
-        <v>343167.05</v>
+        <v>408244.89</v>
       </c>
       <c r="C34" t="n">
-        <v>343167.05</v>
+        <v>408244.89</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -5654,19 +6067,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>46247</v>
+        <v>46188</v>
       </c>
       <c r="B35" t="n">
-        <v>351484.24</v>
+        <v>439289.24</v>
       </c>
       <c r="C35" t="n">
-        <v>351484.24</v>
+        <v>439289.24</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -5678,22 +6091,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>46248</v>
+        <v>46189</v>
       </c>
       <c r="B36" t="n">
-        <v>367007.01</v>
+        <v>478602.6</v>
       </c>
       <c r="C36" t="n">
-        <v>367007.01</v>
+        <v>478602.6</v>
       </c>
       <c r="D36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5702,19 +6115,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>46251</v>
+        <v>46190</v>
       </c>
       <c r="B37" t="n">
-        <v>373344.12</v>
+        <v>626856.3100000001</v>
       </c>
       <c r="C37" t="n">
-        <v>373344.12</v>
+        <v>626856.3100000001</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -5726,22 +6139,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>46252</v>
+        <v>46191</v>
       </c>
       <c r="B38" t="n">
-        <v>363374.57</v>
+        <v>586301.61</v>
       </c>
       <c r="C38" t="n">
-        <v>363374.57</v>
+        <v>586301.61</v>
       </c>
       <c r="D38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5750,22 +6163,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>46253</v>
+        <v>46192</v>
       </c>
       <c r="B39" t="n">
-        <v>316490.9</v>
+        <v>691505.27</v>
       </c>
       <c r="C39" t="n">
-        <v>316490.9</v>
+        <v>691505.27</v>
       </c>
       <c r="D39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5774,19 +6187,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>46254</v>
+        <v>46195</v>
       </c>
       <c r="B40" t="n">
-        <v>295714.68</v>
+        <v>695916.11</v>
       </c>
       <c r="C40" t="n">
-        <v>295714.68</v>
+        <v>695916.11</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -5798,19 +6211,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>46255</v>
+        <v>46196</v>
       </c>
       <c r="B41" t="n">
-        <v>318926.89</v>
+        <v>510414.05</v>
       </c>
       <c r="C41" t="n">
-        <v>318926.89</v>
+        <v>510414.05</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -5822,19 +6235,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>46258</v>
+        <v>46197</v>
       </c>
       <c r="B42" t="n">
-        <v>306590.8</v>
+        <v>560010.89</v>
       </c>
       <c r="C42" t="n">
-        <v>306590.8</v>
+        <v>560010.89</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -5846,19 +6259,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>46259</v>
+        <v>46198</v>
       </c>
       <c r="B43" t="n">
-        <v>277660.1</v>
+        <v>540857.7</v>
       </c>
       <c r="C43" t="n">
-        <v>277660.1</v>
+        <v>540857.7</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -5870,19 +6283,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>46260</v>
+        <v>46202</v>
       </c>
       <c r="B44" t="n">
-        <v>332539.05</v>
+        <v>653415.62</v>
       </c>
       <c r="C44" t="n">
-        <v>332539.05</v>
+        <v>653415.62</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -5894,19 +6307,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>46261</v>
+        <v>46203</v>
       </c>
       <c r="B45" t="n">
-        <v>335335.27</v>
+        <v>691322.45</v>
       </c>
       <c r="C45" t="n">
-        <v>335335.27</v>
+        <v>691322.45</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -5918,19 +6331,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>46262</v>
+        <v>46209</v>
       </c>
       <c r="B46" t="n">
-        <v>397365.42</v>
+        <v>630685.38</v>
       </c>
       <c r="C46" t="n">
-        <v>397365.42</v>
+        <v>630685.38</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -5942,22 +6355,22 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>46265</v>
+        <v>46210</v>
       </c>
       <c r="B47" t="n">
-        <v>371553.78</v>
+        <v>491387.72</v>
       </c>
       <c r="C47" t="n">
-        <v>371553.78</v>
+        <v>491387.72</v>
       </c>
       <c r="D47" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5966,19 +6379,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>46266</v>
+        <v>46211</v>
       </c>
       <c r="B48" t="n">
-        <v>253663.41</v>
+        <v>348776.67</v>
       </c>
       <c r="C48" t="n">
-        <v>253663.41</v>
+        <v>348776.67</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -5990,19 +6403,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>46267</v>
+        <v>46212</v>
       </c>
       <c r="B49" t="n">
-        <v>276310.36</v>
+        <v>360847.88</v>
       </c>
       <c r="C49" t="n">
-        <v>276310.36</v>
+        <v>360847.88</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -6014,19 +6427,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>46268</v>
+        <v>46213</v>
       </c>
       <c r="B50" t="n">
-        <v>285566.11</v>
+        <v>427360.86</v>
       </c>
       <c r="C50" t="n">
-        <v>285566.11</v>
+        <v>427360.86</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -6038,31 +6451,943 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B51" t="n">
+        <v>476403.1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>476403.1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B52" t="n">
+        <v>508312.92</v>
+      </c>
+      <c r="C52" t="n">
+        <v>508312.92</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B53" t="n">
+        <v>520872.01</v>
+      </c>
+      <c r="C53" t="n">
+        <v>520872.01</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B54" t="n">
+        <v>597074.76</v>
+      </c>
+      <c r="C54" t="n">
+        <v>597074.76</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B55" t="n">
+        <v>383055.85</v>
+      </c>
+      <c r="C55" t="n">
+        <v>383055.85</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B56" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="C56" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B57" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="C57" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B58" t="n">
+        <v>394650.02</v>
+      </c>
+      <c r="C58" t="n">
+        <v>394650.02</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B59" t="n">
+        <v>281378.71</v>
+      </c>
+      <c r="C59" t="n">
+        <v>281378.71</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B60" t="n">
+        <v>187120.58</v>
+      </c>
+      <c r="C60" t="n">
+        <v>187120.58</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B61" t="n">
+        <v>185777.83</v>
+      </c>
+      <c r="C61" t="n">
+        <v>185777.83</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B62" t="n">
+        <v>191241.28</v>
+      </c>
+      <c r="C62" t="n">
+        <v>191241.28</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B63" t="n">
+        <v>201205.73</v>
+      </c>
+      <c r="C63" t="n">
+        <v>201205.73</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B64" t="n">
+        <v>218562.88</v>
+      </c>
+      <c r="C64" t="n">
+        <v>218562.88</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B65" t="n">
+        <v>260072.7</v>
+      </c>
+      <c r="C65" t="n">
+        <v>260072.7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B66" t="n">
+        <v>350945.98</v>
+      </c>
+      <c r="C66" t="n">
+        <v>350945.98</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B67" t="n">
+        <v>335695.17</v>
+      </c>
+      <c r="C67" t="n">
+        <v>335695.17</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B68" t="n">
+        <v>376597.84</v>
+      </c>
+      <c r="C68" t="n">
+        <v>376597.84</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B69" t="n">
+        <v>385163.61</v>
+      </c>
+      <c r="C69" t="n">
+        <v>385163.61</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B70" t="n">
+        <v>318603.79</v>
+      </c>
+      <c r="C70" t="n">
+        <v>318603.79</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B71" t="n">
+        <v>363157.68</v>
+      </c>
+      <c r="C71" t="n">
+        <v>363157.68</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B72" t="n">
+        <v>343167.05</v>
+      </c>
+      <c r="C72" t="n">
+        <v>343167.05</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B73" t="n">
+        <v>351484.24</v>
+      </c>
+      <c r="C73" t="n">
+        <v>351484.24</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B74" t="n">
+        <v>367007.01</v>
+      </c>
+      <c r="C74" t="n">
+        <v>367007.01</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B75" t="n">
+        <v>373344.12</v>
+      </c>
+      <c r="C75" t="n">
+        <v>373344.12</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B76" t="n">
+        <v>363374.57</v>
+      </c>
+      <c r="C76" t="n">
+        <v>363374.57</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B77" t="n">
+        <v>316490.9</v>
+      </c>
+      <c r="C77" t="n">
+        <v>316490.9</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B78" t="n">
+        <v>295714.68</v>
+      </c>
+      <c r="C78" t="n">
+        <v>295714.68</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B79" t="n">
+        <v>318926.89</v>
+      </c>
+      <c r="C79" t="n">
+        <v>318926.89</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B80" t="n">
+        <v>306590.8</v>
+      </c>
+      <c r="C80" t="n">
+        <v>306590.8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B81" t="n">
+        <v>277660.1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>277660.1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B82" t="n">
+        <v>332539.05</v>
+      </c>
+      <c r="C82" t="n">
+        <v>332539.05</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B83" t="n">
+        <v>335335.27</v>
+      </c>
+      <c r="C83" t="n">
+        <v>335335.27</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B84" t="n">
+        <v>397365.42</v>
+      </c>
+      <c r="C84" t="n">
+        <v>397365.42</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B85" t="n">
+        <v>371553.78</v>
+      </c>
+      <c r="C85" t="n">
+        <v>371553.78</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B86" t="n">
+        <v>253663.41</v>
+      </c>
+      <c r="C86" t="n">
+        <v>253663.41</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B87" t="n">
+        <v>276310.36</v>
+      </c>
+      <c r="C87" t="n">
+        <v>276310.36</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B88" t="n">
+        <v>285566.11</v>
+      </c>
+      <c r="C88" t="n">
+        <v>285566.11</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B89" t="n">
         <v>330656.93</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C89" t="n">
         <v>330656.93</v>
       </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>new SOF series (2026-07-06..09-05)</t>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SOF-stated (quarterly 04-01..06-30 + 9 weeklies 07-06..09-05)</t>
         </is>
       </c>
     </row>
@@ -6105,12 +7430,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GATE1_weekly_points</t>
+          <t>GATE1_anchor_points</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50/50 exact</t>
+          <t>88/88 exact</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6132,7 +7457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>min balance Rs 0.00</t>
+          <t>min balance Rs 53,282.07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6149,22 +7474,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GATE2_interest_ADVISORY</t>
+          <t>GATE2_rate_consistency</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>advisory Rs 13,149.75</t>
+          <t>see MONTHLY_RATE sheet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>vs SOF-billed Rs 6,150.79 over the SOF-covered window</t>
+          <t>advisory 9.49% flat vs SOF-billed, monthly</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FINDING (demoted per Chat; never plugged)</t>
+          <t>FINDING</t>
         </is>
       </c>
     </row>
@@ -6176,17 +7501,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rs 8,142.00 DN-basis</t>
+          <t>Rs 21,210.50 DN-basis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-06..09-05 only; 2026-04-27..07-05 has no SOF on device</t>
+          <t>2026-04-29..2026-09-05; only 2026-07-01..07-05 uncovered</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PARTIAL (G2 half-closed)</t>
+          <t>PASS (G2 closed)</t>
         </is>
       </c>
     </row>
@@ -6201,7 +7526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6224,7 +7549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M1b PASS - GATE1 canonical loan liability; extended to 2026-09-05 from 9 weekly SOFs</t>
+          <t>Full MTF era SOF-sourced. Quarterly SOF 2026-04-01..06-30 + 9 weeklies 07-06..09-05.</t>
         </is>
       </c>
     </row>
@@ -6236,67 +7561,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MA-EQUITY financing = SOF-BILLED (interest + pledge), NOT the advisory accrual. CANONICAL total over the SOF-covered window 2026-07-06..2026-09-05: interest Rs 6,150.79 + pledge Rs 8,142.00 (DN basis) = Rs 14,292.79. Plus the previously billed interest Rs 4,321.62 to 2026-06-19. This SUPERSEDES the interest-only figure Rs 9,725.92 reported in Task 1b, which is now withdrawn as incomplete.</t>
+          <t>MA-EQUITY financing = SOF-BILLED (interest + pledge). At the register cutoff 2026-08-28: interest Rs 11,356.01 + pledge Rs 20,237.00 = Rs 31,593.01. ONE figure, no range. Supersedes Rs 12,620.38 and the Rs 16,942.00 ceiling.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pledge_basis</t>
+          <t>pre_Jun19_interest</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DN = SOF x 1.18 (DebitNote_VERIFIED). Corroborated in-file: a 225.00 pledge debit is mirrored by a 265.50 "GST and MTF pledge Charges recovered" credit.</t>
+          <t>The Rs 4,321.62 previously carried as "known but outside granularity" is now SUBSUMED: SOF-billed interest 2026-04-27..2026-06-19 sums to Rs 4,149.50 from the daily rows. Do NOT add it again.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pledge_gap</t>
+          <t>remaining_gap</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pledge charges for 2026-04-27..2026-07-05 remain UNAVAILABLE - no SOF covering that period was supplied. G2 is HALF-closed, not closed.</t>
+          <t>2026-07-01..07-05 has no SOF (quarterly ends 06-30, weeklies start 07-06). 07-01/07-02 keep their interpolated values; 07-03 keeps its original anchor.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>negatives</t>
+          <t>pledge_basis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eliminated via non-negative waterfall (pro-rata capped + carry-forward), anchors held exact</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>S7 STATUS (Jul 23 2026)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RETAINED VALID - GATE-1 reconstruction is INDEPENDENT of the EQUITY defect. VALID for LOAN LIABILITY use. NOT VALID as an input to MA-NAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>S8 EXTENSION (this run)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-04..2026-09-05 appended. 2026-07-04..07-10 were PROVISIONAL and are UPGRADED from SOF; see CHANGE_LOG. 2026-04-27..07-03 untouched.</t>
+          <t>DN = SOF x 1.18 (DebitNote_VERIFIED).</t>
         </is>
       </c>
     </row>
@@ -6311,7 +7612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6348,69 +7649,69 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46207</v>
+        <v>46139</v>
       </c>
       <c r="B2" t="n">
-        <v>618861.6899999999</v>
+        <v>51447.2</v>
       </c>
       <c r="C2" t="n">
-        <v>618861.6899999999</v>
+        <v>70105.10000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
+          <t>PRE-SERIES</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SOF-EXACT(weekend, proven by Jul-06 opening)</t>
+          <t>SOF-EXACT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>value unchanged; tag upgraded from PROVISIONAL to verified</t>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46208</v>
+        <v>46140</v>
       </c>
       <c r="B3" t="n">
-        <v>618861.6899999999</v>
+        <v>173594.8</v>
       </c>
       <c r="C3" t="n">
-        <v>618861.6899999999</v>
+        <v>147526.44</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
+          <t>PRE-SERIES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SOF-EXACT(weekend, proven by Jul-06 opening)</t>
+          <t>SOF-EXACT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>value unchanged; tag upgraded from PROVISIONAL to verified</t>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46209</v>
+        <v>46141</v>
       </c>
       <c r="B4" t="n">
-        <v>618861.6899999999</v>
+        <v>304779.21</v>
       </c>
       <c r="C4" t="n">
-        <v>630685.38</v>
+        <v>259615.29</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
+          <t>PRE-SERIES</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6420,23 +7721,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy) superseded by SOF-stated EOD balance</t>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46210</v>
+        <v>46142</v>
       </c>
       <c r="B5" t="n">
-        <v>618861.6899999999</v>
+        <v>257617.38</v>
       </c>
       <c r="C5" t="n">
-        <v>491387.72</v>
+        <v>203852.43</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
+          <t>PRE-SERIES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6446,85 +7747,2601 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy) superseded by SOF-stated EOD balance</t>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46211</v>
+        <v>46143</v>
       </c>
       <c r="B6" t="n">
-        <v>618861.6899999999</v>
+        <v>257617.38</v>
       </c>
       <c r="C6" t="n">
-        <v>348776.67</v>
+        <v>203852.43</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
+          <t>PRE-SERIES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOF-EXACT</t>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PROVISIONAL(Jul-03 proxy) superseded by SOF-stated EOD balance</t>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46212</v>
+        <v>46144</v>
+      </c>
+      <c r="B7" t="n">
+        <v>257617.38</v>
+      </c>
+      <c r="C7" t="n">
+        <v>203852.43</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B8" t="n">
+        <v>257617.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>203852.43</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B9" t="n">
+        <v>354289.66</v>
+      </c>
+      <c r="C9" t="n">
+        <v>323414.38</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B10" t="n">
+        <v>322794.14</v>
+      </c>
+      <c r="C10" t="n">
+        <v>290619.32</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B11" t="n">
+        <v>294026.97</v>
+      </c>
+      <c r="C11" t="n">
+        <v>259027.83</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B12" t="n">
+        <v>327520.73</v>
+      </c>
+      <c r="C12" t="n">
+        <v>288661.63</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B13" t="n">
+        <v>416406</v>
+      </c>
+      <c r="C13" t="n">
+        <v>414936.19</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B14" t="n">
+        <v>416406</v>
+      </c>
+      <c r="C14" t="n">
+        <v>414936.19</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B15" t="n">
+        <v>416406</v>
+      </c>
+      <c r="C15" t="n">
+        <v>414936.19</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B16" t="n">
+        <v>461408.05</v>
+      </c>
+      <c r="C16" t="n">
+        <v>428994.67</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>54502.96</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B18" t="n">
+        <v>128971.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>107396.66</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B19" t="n">
+        <v>302.88</v>
+      </c>
+      <c r="C19" t="n">
+        <v>97655.74000000001</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B20" t="n">
+        <v>16530.88</v>
+      </c>
+      <c r="C20" t="n">
+        <v>105364.04</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B21" t="n">
+        <v>16530.88</v>
+      </c>
+      <c r="C21" t="n">
+        <v>105364.04</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B22" t="n">
+        <v>16530.88</v>
+      </c>
+      <c r="C22" t="n">
+        <v>105364.04</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>83052.91</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B24" t="n">
+        <v>24017.4</v>
+      </c>
+      <c r="C24" t="n">
+        <v>53282.07</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B25" t="n">
+        <v>173707.14</v>
+      </c>
+      <c r="C25" t="n">
+        <v>205417.77</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B26" t="n">
+        <v>408994.69</v>
+      </c>
+      <c r="C26" t="n">
+        <v>401299.48</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B27" t="n">
+        <v>475053.59</v>
+      </c>
+      <c r="C27" t="n">
+        <v>411850.1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B28" t="n">
+        <v>475053.59</v>
+      </c>
+      <c r="C28" t="n">
+        <v>411850.1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B29" t="n">
+        <v>475053.59</v>
+      </c>
+      <c r="C29" t="n">
+        <v>411850.1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B30" t="n">
+        <v>512507.76</v>
+      </c>
+      <c r="C30" t="n">
+        <v>430133.89</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B31" t="n">
+        <v>400041.02</v>
+      </c>
+      <c r="C31" t="n">
+        <v>377941.36</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B32" t="n">
+        <v>396347.83</v>
+      </c>
+      <c r="C32" t="n">
+        <v>382122.93</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B33" t="n">
+        <v>396347.83</v>
+      </c>
+      <c r="C33" t="n">
+        <v>382122.93</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PRE-SERIES</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SOF-CARRY(non-trading day, no MTF rows)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B34" t="n">
+        <v>437502.36</v>
+      </c>
+      <c r="C34" t="n">
+        <v>435243.47</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B35" t="n">
+        <v>495876.29</v>
+      </c>
+      <c r="C35" t="n">
+        <v>487596.85</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B36" t="n">
+        <v>247989.17</v>
+      </c>
+      <c r="C36" t="n">
+        <v>428034.78</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B37" t="n">
+        <v>463717.27</v>
+      </c>
+      <c r="C37" t="n">
+        <v>488217.23</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B38" t="n">
+        <v>544644.49</v>
+      </c>
+      <c r="C38" t="n">
+        <v>557688.8100000001</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B39" t="n">
+        <v>542816.72</v>
+      </c>
+      <c r="C39" t="n">
+        <v>552005.53</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B40" t="n">
+        <v>276185.9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>398661.94</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B41" t="n">
+        <v>197524.69</v>
+      </c>
+      <c r="C41" t="n">
+        <v>287970.17</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B42" t="n">
+        <v>440734.59</v>
+      </c>
+      <c r="C42" t="n">
+        <v>439289.24</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B43" t="n">
+        <v>512823.73</v>
+      </c>
+      <c r="C43" t="n">
+        <v>478602.6</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B44" t="n">
+        <v>714261.25</v>
+      </c>
+      <c r="C44" t="n">
+        <v>626856.3100000001</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B45" t="n">
+        <v>642693.89</v>
+      </c>
+      <c r="C45" t="n">
+        <v>586301.61</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B46" t="n">
+        <v>644690.25</v>
+      </c>
+      <c r="C46" t="n">
+        <v>695916.11</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B47" t="n">
+        <v>473917.83</v>
+      </c>
+      <c r="C47" t="n">
+        <v>510414.05</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B48" t="n">
+        <v>578262.98</v>
+      </c>
+      <c r="C48" t="n">
+        <v>560010.89</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B49" t="n">
+        <v>643261.45</v>
+      </c>
+      <c r="C49" t="n">
+        <v>653415.62</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B50" t="n">
+        <v>724597.04</v>
+      </c>
+      <c r="C50" t="n">
+        <v>691322.45</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>INTERPOLATED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SOF-EXACT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>reconstructed value superseded by SOF-stated EOD balance</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>mon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>interest_accrued_advisory</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>interest_sof_billed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>balance</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>adv_vs_billed_%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>implied_rate_%pa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>177.09</v>
+      </c>
+      <c r="C2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="D2" t="n">
+        <v>170274.815</v>
+      </c>
+      <c r="E2" t="n">
+        <v>855.6900000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2414.84</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1885.96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>299614.6454838709</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28.04</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.41</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4179.82</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3999.64</v>
+      </c>
+      <c r="D4" t="n">
+        <v>535877.7803333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.08</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3277.04</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3179.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>406586.5090322581</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.210000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2733.88</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2538.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>339188.4603225806</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.81</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="C7" t="n">
+        <v>432.59</v>
+      </c>
+      <c r="D7" t="n">
+        <v>295370.748</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>anchor_date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reconstructed</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SOF_LOAN_BALANCE</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B2" t="n">
+        <v>571466.4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>571466.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B3" t="n">
+        <v>578701.49</v>
+      </c>
+      <c r="C3" t="n">
+        <v>578701.49</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B4" t="n">
+        <v>408244.89</v>
+      </c>
+      <c r="C4" t="n">
+        <v>408244.89</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B5" t="n">
+        <v>691505.27</v>
+      </c>
+      <c r="C5" t="n">
+        <v>691505.27</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B6" t="n">
+        <v>540857.7</v>
+      </c>
+      <c r="C6" t="n">
+        <v>540857.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46206</v>
       </c>
       <c r="B7" t="n">
         <v>618861.6899999999</v>
       </c>
       <c r="C7" t="n">
+        <v>618861.6899999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>original (2026-04-27..07-03 window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B8" t="n">
+        <v>630685.38</v>
+      </c>
+      <c r="C8" t="n">
+        <v>630685.38</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B9" t="n">
+        <v>491387.72</v>
+      </c>
+      <c r="C9" t="n">
+        <v>491387.72</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B10" t="n">
+        <v>348776.67</v>
+      </c>
+      <c r="C10" t="n">
+        <v>348776.67</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B11" t="n">
         <v>360847.88</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SOF-EXACT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PROVISIONAL(Jul-03 proxy) superseded by SOF-stated EOD balance</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="C11" t="n">
+        <v>360847.88</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
         <v>46213</v>
       </c>
-      <c r="B8" t="n">
-        <v>618861.6899999999</v>
-      </c>
-      <c r="C8" t="n">
+      <c r="B12" t="n">
         <v>427360.86</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PROVISIONAL(Jul-03 proxy)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SOF-EXACT</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>PROVISIONAL(Jul-03 proxy) superseded by SOF-stated EOD balance</t>
+      <c r="C12" t="n">
+        <v>427360.86</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B13" t="n">
+        <v>476403.1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>476403.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B14" t="n">
+        <v>508312.92</v>
+      </c>
+      <c r="C14" t="n">
+        <v>508312.92</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B15" t="n">
+        <v>520872.01</v>
+      </c>
+      <c r="C15" t="n">
+        <v>520872.01</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B16" t="n">
+        <v>597074.76</v>
+      </c>
+      <c r="C16" t="n">
+        <v>597074.76</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B17" t="n">
+        <v>383055.85</v>
+      </c>
+      <c r="C17" t="n">
+        <v>383055.85</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B18" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="C18" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B19" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="C19" t="n">
+        <v>407769.28</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B20" t="n">
+        <v>394650.02</v>
+      </c>
+      <c r="C20" t="n">
+        <v>394650.02</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B21" t="n">
+        <v>281378.71</v>
+      </c>
+      <c r="C21" t="n">
+        <v>281378.71</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B22" t="n">
+        <v>187120.58</v>
+      </c>
+      <c r="C22" t="n">
+        <v>187120.58</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B23" t="n">
+        <v>185777.83</v>
+      </c>
+      <c r="C23" t="n">
+        <v>185777.83</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B24" t="n">
+        <v>191241.28</v>
+      </c>
+      <c r="C24" t="n">
+        <v>191241.28</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B25" t="n">
+        <v>201205.73</v>
+      </c>
+      <c r="C25" t="n">
+        <v>201205.73</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B26" t="n">
+        <v>218562.88</v>
+      </c>
+      <c r="C26" t="n">
+        <v>218562.88</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B27" t="n">
+        <v>260072.7</v>
+      </c>
+      <c r="C27" t="n">
+        <v>260072.7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B28" t="n">
+        <v>350945.98</v>
+      </c>
+      <c r="C28" t="n">
+        <v>350945.98</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B29" t="n">
+        <v>335695.17</v>
+      </c>
+      <c r="C29" t="n">
+        <v>335695.17</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B30" t="n">
+        <v>376597.84</v>
+      </c>
+      <c r="C30" t="n">
+        <v>376597.84</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B31" t="n">
+        <v>385163.61</v>
+      </c>
+      <c r="C31" t="n">
+        <v>385163.61</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B32" t="n">
+        <v>318603.79</v>
+      </c>
+      <c r="C32" t="n">
+        <v>318603.79</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B33" t="n">
+        <v>363157.68</v>
+      </c>
+      <c r="C33" t="n">
+        <v>363157.68</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B34" t="n">
+        <v>343167.05</v>
+      </c>
+      <c r="C34" t="n">
+        <v>343167.05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B35" t="n">
+        <v>351484.24</v>
+      </c>
+      <c r="C35" t="n">
+        <v>351484.24</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B36" t="n">
+        <v>367007.01</v>
+      </c>
+      <c r="C36" t="n">
+        <v>367007.01</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B37" t="n">
+        <v>373344.12</v>
+      </c>
+      <c r="C37" t="n">
+        <v>373344.12</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B38" t="n">
+        <v>363374.57</v>
+      </c>
+      <c r="C38" t="n">
+        <v>363374.57</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B39" t="n">
+        <v>316490.9</v>
+      </c>
+      <c r="C39" t="n">
+        <v>316490.9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B40" t="n">
+        <v>295714.68</v>
+      </c>
+      <c r="C40" t="n">
+        <v>295714.68</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B41" t="n">
+        <v>318926.89</v>
+      </c>
+      <c r="C41" t="n">
+        <v>318926.89</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B42" t="n">
+        <v>306590.8</v>
+      </c>
+      <c r="C42" t="n">
+        <v>306590.8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B43" t="n">
+        <v>277660.1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>277660.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B44" t="n">
+        <v>332539.05</v>
+      </c>
+      <c r="C44" t="n">
+        <v>332539.05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B45" t="n">
+        <v>335335.27</v>
+      </c>
+      <c r="C45" t="n">
+        <v>335335.27</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B46" t="n">
+        <v>397365.42</v>
+      </c>
+      <c r="C46" t="n">
+        <v>397365.42</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B47" t="n">
+        <v>371553.78</v>
+      </c>
+      <c r="C47" t="n">
+        <v>371553.78</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B48" t="n">
+        <v>253663.41</v>
+      </c>
+      <c r="C48" t="n">
+        <v>253663.41</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B49" t="n">
+        <v>276310.36</v>
+      </c>
+      <c r="C49" t="n">
+        <v>276310.36</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B50" t="n">
+        <v>285566.11</v>
+      </c>
+      <c r="C50" t="n">
+        <v>285566.11</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B51" t="n">
+        <v>330656.93</v>
+      </c>
+      <c r="C51" t="n">
+        <v>330656.93</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>new SOF series (2026-07-06..09-05)</t>
         </is>
       </c>
     </row>
